--- a/DATRAS/Results/Sepiidae/Sepiidae_TrendTable.xlsx
+++ b/DATRAS/Results/Sepiidae/Sepiidae_TrendTable.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -504,44 +504,39 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>North Sea</t>
+          <t>English Channel</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>IBTS Q1</t>
+          <t>BTS Q1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>↗</t>
+          <t>↘</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>↗</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>↘</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>North Sea</t>
+          <t>English Channel</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IBTS Q3</t>
+          <t>FR-WCGFS</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>↘</t>
+          <t>↗</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -553,64 +548,49 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>North Sea</t>
+          <t>English Channel</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BTS</t>
+          <t>BTS Q3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>↗</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>↘</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>North Sea</t>
+          <t>English Channel</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DYFS</t>
+          <t>FR-CGFS</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>↗</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>↗</t>
+          <t>↘</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>North Sea</t>
+          <t>English Channel</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>IBTS Q1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
-        <is>
-          <t>↗</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
         <is>
           <t>↗</t>
         </is>
@@ -619,7 +599,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>English Channel</t>
+          <t>Celtic Seas</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -629,7 +609,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>↘</t>
+          <t>↗</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -641,54 +621,59 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>English Channel</t>
+          <t>Celtic Seas</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>FR-WCGFS</t>
+          <t>EVHOE</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>↗</t>
+          <t>↘</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>↗</t>
+          <t>↘</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>English Channel</t>
+          <t>Celtic Seas</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BTS Q3</t>
+          <t>IE-IGFS</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>↗</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>↗</t>
+          <t>↘</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>English Channel</t>
+          <t>Celtic Seas</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FR-CGFS</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+          <t>SCOWCGFS Q1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>↘</t>
         </is>
@@ -697,17 +682,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>English Channel</t>
+          <t>Celtic Seas</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>IBTS Q1</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>↗</t>
+          <t>SCOWCGFS Q4</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>↘</t>
         </is>
       </c>
     </row>
@@ -719,17 +704,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BTS Q1</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>↗</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>↗</t>
+          <t>SP-PORC</t>
         </is>
       </c>
     </row>
@@ -741,34 +716,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>EVHOE</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>↘</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>↘</t>
+          <t>NIGFS Q1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Celtic Seas</t>
+          <t>Bay of Biscay</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>IE-IGFS</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>↗</t>
+          <t>BTS-VIII</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -780,32 +740,42 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Celtic Seas</t>
+          <t>Bay of Biscay</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SCOWCGFS Q1</t>
+          <t>EVHOE</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
           <t>↘</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Celtic Seas</t>
+          <t>Bay of Biscay</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SCOWCGFS Q4</t>
+          <t>SP-NORTH</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
+        <is>
+          <t>↘</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>↘</t>
         </is>
@@ -814,122 +784,37 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Celtic Seas</t>
+          <t>Western Iberia &amp; Gulf of Cadiz</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SP-PORC</t>
+          <t>SP-ARSA Q4</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>↘</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>↗</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Celtic Seas</t>
+          <t>Western Iberia &amp; Gulf of Cadiz</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NIGFS Q1</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Bay of Biscay</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>BTS-VIII</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>↘</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Bay of Biscay</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>EVHOE</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>↘</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Bay of Biscay</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
           <t>SP-NORTH</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>↘</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>↘</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Western Iberia &amp; Gulf of Cadiz</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>SP-ARSA Q4</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>↘</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Western Iberia &amp; Gulf of Cadiz</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>SP-NORTH</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>↘</t>
         </is>
